--- a/docs/downloads/04/tbl_homeland_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/04/tbl_homeland_marovoay_ampijoroa.xlsx
@@ -397,12 +397,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -420,12 +414,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -466,12 +454,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -488,12 +470,6 @@
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
       </c>
     </row>
     <row r="7">
